--- a/reviews/a-envoyer/la-galerie-immobiliere-2026-10-05.xlsx
+++ b/reviews/a-envoyer/la-galerie-immobiliere-2026-10-05.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02T06:15:02</t>
+          <t>2026-10-02T10:58:09</t>
         </is>
       </c>
     </row>
